--- a/case_studies/current_layout_optimal/technologies.xlsx
+++ b/case_studies/current_layout_optimal/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\current_layout_optimal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87DF909-DA3E-417E-B292-592910BB6F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EDB133A-5DED-4990-8496-CCBF2814FD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="38">
   <si>
     <t>cluster</t>
   </si>
@@ -120,6 +120,21 @@
   </si>
   <si>
     <t>NL4</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_BE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_DE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_NL</t>
+  </si>
+  <si>
+    <t>H2_network_connection_in</t>
+  </si>
+  <si>
+    <t>H2_network_connection_out</t>
   </si>
 </sst>
 </file>
@@ -517,8 +532,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -546,7 +561,7 @@
     <col min="25" max="26" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -625,8 +640,23 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
@@ -705,8 +735,23 @@
       <c r="Z2" s="3">
         <v>0</v>
       </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -785,8 +830,23 @@
       <c r="Z3" s="5">
         <v>44.5</v>
       </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -865,8 +925,23 @@
       <c r="Z4" s="3">
         <v>38.94</v>
       </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
@@ -945,8 +1020,23 @@
       <c r="Z5" s="5">
         <v>211.38</v>
       </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -1025,8 +1115,23 @@
       <c r="Z6" s="3">
         <v>0</v>
       </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
@@ -1105,8 +1210,23 @@
       <c r="Z7" s="5">
         <v>0</v>
       </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -1183,6 +1303,21 @@
         <v>0</v>
       </c>
       <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
         <v>0</v>
       </c>
     </row>
@@ -1193,8 +1328,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E67A4DCA-0F0C-49CF-991F-4B75153ECE5A}">
-  <dimension ref="A1:Z8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -1222,7 +1357,7 @@
     <col min="25" max="26" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1301,8 +1436,23 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
@@ -1381,8 +1531,23 @@
       <c r="Z2" s="3">
         <v>1</v>
       </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -1461,8 +1626,23 @@
       <c r="Z3" s="5">
         <v>1</v>
       </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -1541,8 +1721,23 @@
       <c r="Z4" s="3">
         <v>1</v>
       </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>1</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
@@ -1621,8 +1816,23 @@
       <c r="Z5" s="5">
         <v>1</v>
       </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -1701,8 +1911,23 @@
       <c r="Z6" s="3">
         <v>1</v>
       </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
@@ -1781,8 +2006,23 @@
       <c r="Z7" s="5">
         <v>1</v>
       </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -1860,6 +2100,21 @@
       </c>
       <c r="Z8" s="3">
         <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/case_studies/current_layout_optimal/technologies.xlsx
+++ b/case_studies/current_layout_optimal/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\current_layout_optimal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EDB133A-5DED-4990-8496-CCBF2814FD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50FCE0B-5D92-405B-8CDA-5FCC80B3BF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -101,6 +101,21 @@
     <t>CO2toEmissions</t>
   </si>
   <si>
+    <t>electricity_grid_connection_BE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_DE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_NL</t>
+  </si>
+  <si>
+    <t>H2_network_connection_in</t>
+  </si>
+  <si>
+    <t>H2_network_connection_out</t>
+  </si>
+  <si>
     <t>BEL1</t>
   </si>
   <si>
@@ -120,21 +135,6 @@
   </si>
   <si>
     <t>NL4</t>
-  </si>
-  <si>
-    <t>electricity_grid_connection_BE</t>
-  </si>
-  <si>
-    <t>electricity_grid_connection_DE</t>
-  </si>
-  <si>
-    <t>electricity_grid_connection_NL</t>
-  </si>
-  <si>
-    <t>H2_network_connection_in</t>
-  </si>
-  <si>
-    <t>H2_network_connection_out</t>
   </si>
 </sst>
 </file>
@@ -533,7 +533,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -559,9 +559,12 @@
     <col min="23" max="23" width="11" customWidth="1"/>
     <col min="24" max="24" width="15" customWidth="1"/>
     <col min="25" max="26" width="16" customWidth="1"/>
+    <col min="27" max="29" width="32" customWidth="1"/>
+    <col min="30" max="30" width="26" customWidth="1"/>
+    <col min="31" max="31" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -640,25 +643,25 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>37</v>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
@@ -735,25 +738,25 @@
       <c r="Z2" s="3">
         <v>0</v>
       </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
+      <c r="AA2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B3" s="5">
         <v>0</v>
@@ -830,25 +833,25 @@
       <c r="Z3" s="5">
         <v>44.5</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
+      <c r="AA3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -875,7 +878,7 @@
         <v>31.03</v>
       </c>
       <c r="J4" s="3">
-        <v>75.989999999999995</v>
+        <v>146.74</v>
       </c>
       <c r="K4" s="3">
         <v>30.09</v>
@@ -884,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="M4" s="3">
-        <v>515.11</v>
+        <v>1369.36</v>
       </c>
       <c r="N4" s="3">
-        <v>515.11</v>
+        <v>1369.36</v>
       </c>
       <c r="O4" s="3">
         <v>0</v>
@@ -905,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="T4" s="3">
-        <v>31.03</v>
+        <v>76.680000000000007</v>
       </c>
       <c r="U4" s="3">
         <v>0</v>
@@ -917,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="X4" s="3">
-        <v>0</v>
+        <v>369.36</v>
       </c>
       <c r="Y4" s="3">
         <v>0</v>
@@ -925,25 +928,25 @@
       <c r="Z4" s="3">
         <v>38.94</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
+      <c r="AA4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B5" s="5">
         <v>0</v>
@@ -970,7 +973,7 @@
         <v>84.32</v>
       </c>
       <c r="J5" s="5">
-        <v>78.08</v>
+        <v>139.82</v>
       </c>
       <c r="K5" s="5">
         <v>163.36000000000001</v>
@@ -979,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>745.4</v>
       </c>
       <c r="N5" s="5">
-        <v>0</v>
+        <v>745.4</v>
       </c>
       <c r="O5" s="5">
         <v>0</v>
@@ -1020,25 +1023,25 @@
       <c r="Z5" s="5">
         <v>211.38</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
+      <c r="AA5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
@@ -1115,25 +1118,25 @@
       <c r="Z6" s="3">
         <v>0</v>
       </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
+      <c r="AA6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B7" s="5">
         <v>0</v>
@@ -1210,25 +1213,25 @@
       <c r="Z7" s="5">
         <v>0</v>
       </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
+      <c r="AA7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
@@ -1305,19 +1308,19 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1327,9 +1330,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E67A4DCA-0F0C-49CF-991F-4B75153ECE5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED659418-9862-4053-A5F2-E69F136658B0}">
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -1355,9 +1358,12 @@
     <col min="23" max="23" width="11" customWidth="1"/>
     <col min="24" max="24" width="15" customWidth="1"/>
     <col min="25" max="26" width="16" customWidth="1"/>
+    <col min="27" max="29" width="32" customWidth="1"/>
+    <col min="30" max="30" width="26" customWidth="1"/>
+    <col min="31" max="31" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1436,596 +1442,596 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3">
+        <v>1</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1</v>
+      </c>
+      <c r="K2" s="3">
+        <v>1</v>
+      </c>
+      <c r="L2" s="3">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3">
+        <v>1</v>
+      </c>
+      <c r="N2" s="3">
+        <v>1</v>
+      </c>
+      <c r="O2" s="3">
+        <v>1</v>
+      </c>
+      <c r="P2" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3">
+        <v>1</v>
+      </c>
+      <c r="S2" s="3">
+        <v>1</v>
+      </c>
+      <c r="T2" s="3">
+        <v>1</v>
+      </c>
+      <c r="U2" s="3">
+        <v>1</v>
+      </c>
+      <c r="V2" s="3">
+        <v>1</v>
+      </c>
+      <c r="W2" s="3">
+        <v>1</v>
+      </c>
+      <c r="X2" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1</v>
+      </c>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>1</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+      <c r="T3" s="5">
+        <v>1</v>
+      </c>
+      <c r="U3" s="5">
+        <v>1</v>
+      </c>
+      <c r="V3" s="5">
+        <v>1</v>
+      </c>
+      <c r="W3" s="5">
+        <v>1</v>
+      </c>
+      <c r="X3" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1</v>
+      </c>
+      <c r="L4" s="3">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3">
+        <v>1</v>
+      </c>
+      <c r="N4" s="3">
+        <v>1</v>
+      </c>
+      <c r="O4" s="3">
+        <v>1</v>
+      </c>
+      <c r="P4" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>1</v>
+      </c>
+      <c r="R4" s="3">
+        <v>1</v>
+      </c>
+      <c r="S4" s="3">
+        <v>1</v>
+      </c>
+      <c r="T4" s="3">
+        <v>1</v>
+      </c>
+      <c r="U4" s="3">
+        <v>1</v>
+      </c>
+      <c r="V4" s="3">
+        <v>1</v>
+      </c>
+      <c r="W4" s="3">
+        <v>1</v>
+      </c>
+      <c r="X4" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
+      <c r="T5" s="5">
+        <v>1</v>
+      </c>
+      <c r="U5" s="5">
+        <v>1</v>
+      </c>
+      <c r="V5" s="5">
+        <v>1</v>
+      </c>
+      <c r="W5" s="5">
+        <v>1</v>
+      </c>
+      <c r="X5" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3">
+        <v>1</v>
+      </c>
+      <c r="L6" s="3">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3">
+        <v>1</v>
+      </c>
+      <c r="N6" s="3">
+        <v>1</v>
+      </c>
+      <c r="O6" s="3">
+        <v>1</v>
+      </c>
+      <c r="P6" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>1</v>
+      </c>
+      <c r="R6" s="3">
+        <v>1</v>
+      </c>
+      <c r="S6" s="3">
+        <v>1</v>
+      </c>
+      <c r="T6" s="3">
+        <v>1</v>
+      </c>
+      <c r="U6" s="3">
+        <v>1</v>
+      </c>
+      <c r="V6" s="3">
+        <v>1</v>
+      </c>
+      <c r="W6" s="3">
+        <v>1</v>
+      </c>
+      <c r="X6" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="B7" s="5">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5">
+        <v>1</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1</v>
+      </c>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>1</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>1</v>
+      </c>
+      <c r="T7" s="5">
+        <v>1</v>
+      </c>
+      <c r="U7" s="5">
+        <v>1</v>
+      </c>
+      <c r="V7" s="5">
+        <v>1</v>
+      </c>
+      <c r="W7" s="5">
+        <v>1</v>
+      </c>
+      <c r="X7" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3">
-        <v>1</v>
-      </c>
-      <c r="I2" s="3">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3">
-        <v>1</v>
-      </c>
-      <c r="K2" s="3">
-        <v>1</v>
-      </c>
-      <c r="L2" s="3">
-        <v>1</v>
-      </c>
-      <c r="M2" s="3">
-        <v>1</v>
-      </c>
-      <c r="N2" s="3">
-        <v>1</v>
-      </c>
-      <c r="O2" s="3">
-        <v>1</v>
-      </c>
-      <c r="P2" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>1</v>
-      </c>
-      <c r="R2" s="3">
-        <v>1</v>
-      </c>
-      <c r="S2" s="3">
-        <v>1</v>
-      </c>
-      <c r="T2" s="3">
-        <v>1</v>
-      </c>
-      <c r="U2" s="3">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3">
-        <v>1</v>
-      </c>
-      <c r="W2" s="3">
-        <v>1</v>
-      </c>
-      <c r="X2" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA2">
-        <v>1</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="5">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
-        <v>1</v>
-      </c>
-      <c r="F3" s="5">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>1</v>
-      </c>
-      <c r="N3" s="5">
-        <v>1</v>
-      </c>
-      <c r="O3" s="5">
-        <v>1</v>
-      </c>
-      <c r="P3" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>1</v>
-      </c>
-      <c r="R3" s="5">
-        <v>1</v>
-      </c>
-      <c r="S3" s="5">
-        <v>1</v>
-      </c>
-      <c r="T3" s="5">
-        <v>1</v>
-      </c>
-      <c r="U3" s="5">
-        <v>1</v>
-      </c>
-      <c r="V3" s="5">
-        <v>1</v>
-      </c>
-      <c r="W3" s="5">
-        <v>1</v>
-      </c>
-      <c r="X3" s="5">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="5">
-        <v>1</v>
-      </c>
-      <c r="AA3">
-        <v>1</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3">
-        <v>1</v>
-      </c>
-      <c r="J4" s="3">
-        <v>1</v>
-      </c>
-      <c r="K4" s="3">
-        <v>1</v>
-      </c>
-      <c r="L4" s="3">
-        <v>1</v>
-      </c>
-      <c r="M4" s="3">
-        <v>1</v>
-      </c>
-      <c r="N4" s="3">
-        <v>1</v>
-      </c>
-      <c r="O4" s="3">
-        <v>1</v>
-      </c>
-      <c r="P4" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>1</v>
-      </c>
-      <c r="R4" s="3">
-        <v>1</v>
-      </c>
-      <c r="S4" s="3">
-        <v>1</v>
-      </c>
-      <c r="T4" s="3">
-        <v>1</v>
-      </c>
-      <c r="U4" s="3">
-        <v>1</v>
-      </c>
-      <c r="V4" s="3">
-        <v>1</v>
-      </c>
-      <c r="W4" s="3">
-        <v>1</v>
-      </c>
-      <c r="X4" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>1</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>1</v>
-      </c>
-      <c r="N5" s="5">
-        <v>1</v>
-      </c>
-      <c r="O5" s="5">
-        <v>1</v>
-      </c>
-      <c r="P5" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="5">
-        <v>1</v>
-      </c>
-      <c r="R5" s="5">
-        <v>1</v>
-      </c>
-      <c r="S5" s="5">
-        <v>1</v>
-      </c>
-      <c r="T5" s="5">
-        <v>1</v>
-      </c>
-      <c r="U5" s="5">
-        <v>1</v>
-      </c>
-      <c r="V5" s="5">
-        <v>1</v>
-      </c>
-      <c r="W5" s="5">
-        <v>1</v>
-      </c>
-      <c r="X5" s="5">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="5">
-        <v>1</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>1</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3">
-        <v>1</v>
-      </c>
-      <c r="K6" s="3">
-        <v>1</v>
-      </c>
-      <c r="L6" s="3">
-        <v>1</v>
-      </c>
-      <c r="M6" s="3">
-        <v>1</v>
-      </c>
-      <c r="N6" s="3">
-        <v>1</v>
-      </c>
-      <c r="O6" s="3">
-        <v>1</v>
-      </c>
-      <c r="P6" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>1</v>
-      </c>
-      <c r="R6" s="3">
-        <v>1</v>
-      </c>
-      <c r="S6" s="3">
-        <v>1</v>
-      </c>
-      <c r="T6" s="3">
-        <v>1</v>
-      </c>
-      <c r="U6" s="3">
-        <v>1</v>
-      </c>
-      <c r="V6" s="3">
-        <v>1</v>
-      </c>
-      <c r="W6" s="3">
-        <v>1</v>
-      </c>
-      <c r="X6" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>1</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="5">
-        <v>1</v>
-      </c>
-      <c r="C7" s="5">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5">
-        <v>1</v>
-      </c>
-      <c r="F7" s="5">
-        <v>1</v>
-      </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5">
-        <v>1</v>
-      </c>
-      <c r="J7" s="5">
-        <v>1</v>
-      </c>
-      <c r="K7" s="5">
-        <v>1</v>
-      </c>
-      <c r="L7" s="5">
-        <v>1</v>
-      </c>
-      <c r="M7" s="5">
-        <v>1</v>
-      </c>
-      <c r="N7" s="5">
-        <v>1</v>
-      </c>
-      <c r="O7" s="5">
-        <v>1</v>
-      </c>
-      <c r="P7" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="5">
-        <v>1</v>
-      </c>
-      <c r="R7" s="5">
-        <v>1</v>
-      </c>
-      <c r="S7" s="5">
-        <v>1</v>
-      </c>
-      <c r="T7" s="5">
-        <v>1</v>
-      </c>
-      <c r="U7" s="5">
-        <v>1</v>
-      </c>
-      <c r="V7" s="5">
-        <v>1</v>
-      </c>
-      <c r="W7" s="5">
-        <v>1</v>
-      </c>
-      <c r="X7" s="5">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="5">
-        <v>1</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>1</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="B8" s="3">
         <v>1</v>
       </c>
@@ -2101,23 +2107,23 @@
       <c r="Z8" s="3">
         <v>1</v>
       </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/case_studies/current_layout_optimal/technologies.xlsx
+++ b/case_studies/current_layout_optimal/technologies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\current_layout_optimal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50FCE0B-5D92-405B-8CDA-5FCC80B3BF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_FDB96DFEBEACD917DC5155D4235BDA1626C6A665" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -533,7 +533,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -564,7 +564,7 @@
     <col min="31" max="31" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -659,7 +659,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
@@ -718,7 +718,7 @@
         <v>0</v>
       </c>
       <c r="T2" s="3">
-        <v>53</v>
+        <v>159.94</v>
       </c>
       <c r="U2" s="3">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>32</v>
       </c>
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
@@ -908,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="T4" s="3">
-        <v>76.680000000000007</v>
+        <v>231.42</v>
       </c>
       <c r="U4" s="3">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="X4" s="3">
-        <v>369.36</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3">
         <v>0</v>
@@ -944,7 +944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>34</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="T5" s="5">
-        <v>84.32</v>
+        <v>125.97</v>
       </c>
       <c r="U5" s="5">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>35</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="T6" s="3">
-        <v>31.66</v>
+        <v>95.54</v>
       </c>
       <c r="U6" s="3">
         <v>0</v>
@@ -1134,7 +1134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>36</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="T8" s="3">
-        <v>36.58</v>
+        <v>110.4</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
@@ -1330,9 +1330,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED659418-9862-4053-A5F2-E69F136658B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -1363,7 +1363,7 @@
     <col min="31" max="31" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>32</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>34</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>35</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>36</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
